--- a/data/nzd0560/nzd0560.xlsx
+++ b/data/nzd0560/nzd0560.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH274"/>
+  <dimension ref="A1:AH275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29747,7 +29747,7 @@
         <v>304.8</v>
       </c>
       <c r="G273" t="n">
-        <v>297.2</v>
+        <v>300.09</v>
       </c>
       <c r="H273" t="n">
         <v>271.87</v>
@@ -29768,16 +29768,16 @@
         <v>304.08</v>
       </c>
       <c r="N273" t="n">
-        <v>307.09</v>
+        <v>316.14</v>
       </c>
       <c r="O273" t="n">
-        <v>308.31</v>
+        <v>318.08</v>
       </c>
       <c r="P273" t="n">
-        <v>309.55</v>
+        <v>320.75</v>
       </c>
       <c r="Q273" t="n">
-        <v>314.43</v>
+        <v>326.09</v>
       </c>
       <c r="R273" t="n">
         <v>330.3</v>
@@ -29855,7 +29855,7 @@
         <v>298.5</v>
       </c>
       <c r="G274" t="n">
-        <v>297.2</v>
+        <v>300.09</v>
       </c>
       <c r="H274" t="n">
         <v>271.87</v>
@@ -29876,16 +29876,16 @@
         <v>300.44</v>
       </c>
       <c r="N274" t="n">
-        <v>300.9</v>
+        <v>316.14</v>
       </c>
       <c r="O274" t="n">
-        <v>304.14</v>
+        <v>318.08</v>
       </c>
       <c r="P274" t="n">
-        <v>302.49</v>
+        <v>320.75</v>
       </c>
       <c r="Q274" t="n">
-        <v>309.93</v>
+        <v>326.09</v>
       </c>
       <c r="R274" t="n">
         <v>326.71</v>
@@ -29912,7 +29912,7 @@
         <v>299.97</v>
       </c>
       <c r="Z274" t="n">
-        <v>305.79</v>
+        <v>308.93</v>
       </c>
       <c r="AA274" t="n">
         <v>326.42</v>
@@ -29936,6 +29936,114 @@
         <v>349.74</v>
       </c>
       <c r="AH274" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>297.82</v>
+      </c>
+      <c r="C275" t="n">
+        <v>304.59</v>
+      </c>
+      <c r="D275" t="n">
+        <v>288.69</v>
+      </c>
+      <c r="E275" t="n">
+        <v>292.78</v>
+      </c>
+      <c r="F275" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="G275" t="n">
+        <v>308.43</v>
+      </c>
+      <c r="H275" t="n">
+        <v>280.22</v>
+      </c>
+      <c r="I275" t="n">
+        <v>260.54</v>
+      </c>
+      <c r="J275" t="n">
+        <v>277.75</v>
+      </c>
+      <c r="K275" t="n">
+        <v>288.97</v>
+      </c>
+      <c r="L275" t="n">
+        <v>297.13</v>
+      </c>
+      <c r="M275" t="n">
+        <v>299.42</v>
+      </c>
+      <c r="N275" t="n">
+        <v>312.32</v>
+      </c>
+      <c r="O275" t="n">
+        <v>319.32</v>
+      </c>
+      <c r="P275" t="n">
+        <v>321.28</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="R275" t="n">
+        <v>320.13</v>
+      </c>
+      <c r="S275" t="n">
+        <v>314.75</v>
+      </c>
+      <c r="T275" t="n">
+        <v>305.15</v>
+      </c>
+      <c r="U275" t="n">
+        <v>298.53</v>
+      </c>
+      <c r="V275" t="n">
+        <v>295.87</v>
+      </c>
+      <c r="W275" t="n">
+        <v>291.79</v>
+      </c>
+      <c r="X275" t="n">
+        <v>296.83</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>296.68</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>307.02</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>327.13</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>330.05</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>360.86</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>359.93</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>358.22</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="AH275" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29952,7 +30060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B279"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32745,6 +32853,16 @@
       </c>
       <c r="B279" t="n">
         <v>-1.16</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -32913,28 +33031,28 @@
         <v>0.1765</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6850447181627151</v>
+        <v>-0.6834641541707314</v>
       </c>
       <c r="J2" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K2" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2280719422284084</v>
+        <v>0.2285969786220402</v>
       </c>
       <c r="M2" t="n">
-        <v>7.590829622430515</v>
+        <v>7.570312254641819</v>
       </c>
       <c r="N2" t="n">
-        <v>94.67578433579591</v>
+        <v>94.34680170840613</v>
       </c>
       <c r="O2" t="n">
-        <v>9.730148217565645</v>
+        <v>9.713228181629738</v>
       </c>
       <c r="P2" t="n">
-        <v>314.0285960878667</v>
+        <v>314.0120827613522</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32991,28 +33109,28 @@
         <v>0.0501</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.290627880560632</v>
+        <v>-1.28636686994261</v>
       </c>
       <c r="J3" t="n">
+        <v>274</v>
+      </c>
+      <c r="K3" t="n">
         <v>273</v>
       </c>
-      <c r="K3" t="n">
-        <v>272</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3423513175768227</v>
+        <v>0.3424450752512828</v>
       </c>
       <c r="M3" t="n">
-        <v>10.75899553912011</v>
+        <v>10.74460769508673</v>
       </c>
       <c r="N3" t="n">
-        <v>192.8441455133441</v>
+        <v>192.2787267879052</v>
       </c>
       <c r="O3" t="n">
-        <v>13.88683353084295</v>
+        <v>13.86646049963383</v>
       </c>
       <c r="P3" t="n">
-        <v>333.2077226835337</v>
+        <v>333.163578452012</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33069,28 +33187,28 @@
         <v>0.0344</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.06177114802661</v>
+        <v>-1.065846806047926</v>
       </c>
       <c r="J4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2645777671985067</v>
+        <v>0.2674758159403682</v>
       </c>
       <c r="M4" t="n">
-        <v>10.67135377570039</v>
+        <v>10.6504519118047</v>
       </c>
       <c r="N4" t="n">
-        <v>186.106637534453</v>
+        <v>185.5454859799738</v>
       </c>
       <c r="O4" t="n">
-        <v>13.64209065848974</v>
+        <v>13.6215082123814</v>
       </c>
       <c r="P4" t="n">
-        <v>323.229576723883</v>
+        <v>323.2722395602586</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33147,28 +33265,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7168071950185679</v>
+        <v>-0.7154686295300848</v>
       </c>
       <c r="J5" t="n">
+        <v>274</v>
+      </c>
+      <c r="K5" t="n">
         <v>273</v>
       </c>
-      <c r="K5" t="n">
-        <v>272</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1824835724171355</v>
+        <v>0.1830742039878184</v>
       </c>
       <c r="M5" t="n">
-        <v>9.512276103699287</v>
+        <v>9.483686751670295</v>
       </c>
       <c r="N5" t="n">
-        <v>137.5183393727455</v>
+        <v>137.0283487241554</v>
       </c>
       <c r="O5" t="n">
-        <v>11.72682136696665</v>
+        <v>11.70591084555813</v>
       </c>
       <c r="P5" t="n">
-        <v>310.1886895613412</v>
+        <v>310.1747397026999</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33225,28 +33343,28 @@
         <v>0.0596</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6238905049179788</v>
+        <v>-0.6206915840717606</v>
       </c>
       <c r="J6" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K6" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1683763769429437</v>
+        <v>0.1679300537353733</v>
       </c>
       <c r="M6" t="n">
-        <v>8.818815548911932</v>
+        <v>8.801325404349987</v>
       </c>
       <c r="N6" t="n">
-        <v>115.6424871295415</v>
+        <v>115.2996005390367</v>
       </c>
       <c r="O6" t="n">
-        <v>10.75371968806801</v>
+        <v>10.73776515570334</v>
       </c>
       <c r="P6" t="n">
-        <v>310.3130986948424</v>
+        <v>310.2799589355536</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33303,28 +33421,28 @@
         <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5617533260505243</v>
+        <v>-0.5437493701626536</v>
       </c>
       <c r="J7" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K7" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1468574354020262</v>
+        <v>0.1377360516900223</v>
       </c>
       <c r="M7" t="n">
-        <v>7.957622556444914</v>
+        <v>8.006086093018665</v>
       </c>
       <c r="N7" t="n">
-        <v>110.9993117443629</v>
+        <v>112.5419880996946</v>
       </c>
       <c r="O7" t="n">
-        <v>10.53562108963505</v>
+        <v>10.60858087114835</v>
       </c>
       <c r="P7" t="n">
-        <v>303.2520352373144</v>
+        <v>303.0669394779442</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33381,28 +33499,28 @@
         <v>0.0326</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7842033491720214</v>
+        <v>-0.778890379660737</v>
       </c>
       <c r="J8" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K8" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1175870791758657</v>
+        <v>0.1169210931650683</v>
       </c>
       <c r="M8" t="n">
-        <v>13.08854122528225</v>
+        <v>13.06658012450737</v>
       </c>
       <c r="N8" t="n">
-        <v>277.2505478874186</v>
+        <v>276.4297832326665</v>
       </c>
       <c r="O8" t="n">
-        <v>16.65084225759822</v>
+        <v>16.62617764949799</v>
       </c>
       <c r="P8" t="n">
-        <v>293.7819549201691</v>
+        <v>293.7268272047771</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33459,28 +33577,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.329045389942192</v>
+        <v>-1.3280211479072</v>
       </c>
       <c r="J9" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1879926334424576</v>
+        <v>0.1889822128937617</v>
       </c>
       <c r="M9" t="n">
-        <v>16.42967202304514</v>
+        <v>16.37303232342395</v>
       </c>
       <c r="N9" t="n">
-        <v>443.6652626314977</v>
+        <v>442.0049483183952</v>
       </c>
       <c r="O9" t="n">
-        <v>21.06336304181974</v>
+        <v>21.02391372505118</v>
       </c>
       <c r="P9" t="n">
-        <v>294.9996531662785</v>
+        <v>294.9887633283241</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33537,28 +33655,28 @@
         <v>0.0409</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3388402034858127</v>
+        <v>-0.342486951212069</v>
       </c>
       <c r="J10" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K10" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01702870429859615</v>
+        <v>0.01751823405040531</v>
       </c>
       <c r="M10" t="n">
-        <v>16.25816008426776</v>
+        <v>16.21808344564881</v>
       </c>
       <c r="N10" t="n">
-        <v>399.6333494664722</v>
+        <v>398.229558081821</v>
       </c>
       <c r="O10" t="n">
-        <v>19.99083163518897</v>
+        <v>19.95568986734914</v>
       </c>
       <c r="P10" t="n">
-        <v>292.1898059528094</v>
+        <v>292.2279863998911</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33615,28 +33733,28 @@
         <v>0.0649</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.299882385535451</v>
+        <v>-1.29123023754884</v>
       </c>
       <c r="J11" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K11" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2245944127156074</v>
+        <v>0.223387829596982</v>
       </c>
       <c r="M11" t="n">
-        <v>14.81770805256436</v>
+        <v>14.79828151849519</v>
       </c>
       <c r="N11" t="n">
-        <v>353.4449238399067</v>
+        <v>352.6966778300753</v>
       </c>
       <c r="O11" t="n">
-        <v>18.80013095273293</v>
+        <v>18.78022038821896</v>
       </c>
       <c r="P11" t="n">
-        <v>311.6699250059974</v>
+        <v>311.5811414924147</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33693,28 +33811,28 @@
         <v>0.1385</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.536653248456523</v>
+        <v>-0.5384476497244017</v>
       </c>
       <c r="J12" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K12" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06770199894259632</v>
+        <v>0.06861329688676465</v>
       </c>
       <c r="M12" t="n">
-        <v>12.1918826670327</v>
+        <v>12.1590975376741</v>
       </c>
       <c r="N12" t="n">
-        <v>238.5589973184567</v>
+        <v>237.7132539672562</v>
       </c>
       <c r="O12" t="n">
-        <v>15.4453552020812</v>
+        <v>15.4179523273117</v>
       </c>
       <c r="P12" t="n">
-        <v>314.2471193457078</v>
+        <v>314.2657087478668</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33771,28 +33889,28 @@
         <v>0.0963</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6532601021414886</v>
+        <v>-0.6482119006428005</v>
       </c>
       <c r="J13" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K13" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1013237054901699</v>
+        <v>0.1005666236641138</v>
       </c>
       <c r="M13" t="n">
-        <v>12.34915636274821</v>
+        <v>12.33297366484026</v>
       </c>
       <c r="N13" t="n">
-        <v>229.3835003119027</v>
+        <v>228.7234898551368</v>
       </c>
       <c r="O13" t="n">
-        <v>15.14541185679355</v>
+        <v>15.12360703850562</v>
       </c>
       <c r="P13" t="n">
-        <v>309.8162747288424</v>
+        <v>309.7644763611552</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33849,28 +33967,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9729042605903337</v>
+        <v>-0.9381681984368584</v>
       </c>
       <c r="J14" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K14" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1493048143783653</v>
+        <v>0.138891803208033</v>
       </c>
       <c r="M14" t="n">
-        <v>14.66614107246223</v>
+        <v>14.82181506408626</v>
       </c>
       <c r="N14" t="n">
-        <v>328.7702756862756</v>
+        <v>334.0772413331371</v>
       </c>
       <c r="O14" t="n">
-        <v>18.13202348570825</v>
+        <v>18.27777998918734</v>
       </c>
       <c r="P14" t="n">
-        <v>312.9688029664592</v>
+        <v>312.6143676234126</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33927,28 +34045,28 @@
         <v>0.0604</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.751929001537161</v>
+        <v>-0.7198598197084449</v>
       </c>
       <c r="J15" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K15" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1235083601145459</v>
+        <v>0.113200745219038</v>
       </c>
       <c r="M15" t="n">
-        <v>12.50974147560268</v>
+        <v>12.63145488302327</v>
       </c>
       <c r="N15" t="n">
-        <v>243.101944301231</v>
+        <v>246.9667328327606</v>
       </c>
       <c r="O15" t="n">
-        <v>15.59172679023177</v>
+        <v>15.71517524028162</v>
       </c>
       <c r="P15" t="n">
-        <v>316.0464195298221</v>
+        <v>315.7169821365119</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34005,28 +34123,28 @@
         <v>0.0507</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6641601050182304</v>
+        <v>-0.6312780963865264</v>
       </c>
       <c r="J16" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K16" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08691061925128252</v>
+        <v>0.07882324622499282</v>
       </c>
       <c r="M16" t="n">
-        <v>13.12417732347581</v>
+        <v>13.24217032585482</v>
       </c>
       <c r="N16" t="n">
-        <v>278.7667881082265</v>
+        <v>281.3032661490923</v>
       </c>
       <c r="O16" t="n">
-        <v>16.69631061367231</v>
+        <v>16.7720978458001</v>
       </c>
       <c r="P16" t="n">
-        <v>320.0369115562996</v>
+        <v>319.6980101573037</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34083,28 +34201,28 @@
         <v>0.0455</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3839319882973671</v>
+        <v>0.4042937912689518</v>
       </c>
       <c r="J17" t="n">
+        <v>274</v>
+      </c>
+      <c r="K17" t="n">
         <v>273</v>
       </c>
-      <c r="K17" t="n">
-        <v>272</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.02353267640305934</v>
+        <v>0.02629465891058191</v>
       </c>
       <c r="M17" t="n">
-        <v>14.0639796336859</v>
+        <v>13.93271675110299</v>
       </c>
       <c r="N17" t="n">
-        <v>368.0820096122946</v>
+        <v>365.7485013198799</v>
       </c>
       <c r="O17" t="n">
-        <v>19.18546349745803</v>
+        <v>19.12455231684862</v>
       </c>
       <c r="P17" t="n">
-        <v>313.4079537964921</v>
+        <v>313.1984389302727</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34161,28 +34279,28 @@
         <v>0.0552</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2160461180208263</v>
+        <v>0.2053878117724964</v>
       </c>
       <c r="J18" t="n">
+        <v>274</v>
+      </c>
+      <c r="K18" t="n">
         <v>273</v>
       </c>
-      <c r="K18" t="n">
-        <v>272</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.0251071092016748</v>
+        <v>0.02273907860509539</v>
       </c>
       <c r="M18" t="n">
-        <v>8.374020043489148</v>
+        <v>8.398268071618183</v>
       </c>
       <c r="N18" t="n">
-        <v>109.2283942155316</v>
+        <v>109.710309574515</v>
       </c>
       <c r="O18" t="n">
-        <v>10.45123888424389</v>
+        <v>10.47426892792595</v>
       </c>
       <c r="P18" t="n">
-        <v>329.9035049537205</v>
+        <v>330.0139254104697</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34239,28 +34357,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.01141768140390829</v>
+        <v>-0.02074195230628416</v>
       </c>
       <c r="J19" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K19" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L19" t="n">
-        <v>7.30737508999324e-05</v>
+        <v>0.0002414824537597671</v>
       </c>
       <c r="M19" t="n">
-        <v>8.286909599370233</v>
+        <v>8.312380500632678</v>
       </c>
       <c r="N19" t="n">
-        <v>107.3044463132645</v>
+        <v>107.5854337939397</v>
       </c>
       <c r="O19" t="n">
-        <v>10.35878594784469</v>
+        <v>10.37233984180714</v>
       </c>
       <c r="P19" t="n">
-        <v>328.7133744765558</v>
+        <v>328.8099708314214</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34317,28 +34435,28 @@
         <v>0.0559</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2390173863601939</v>
+        <v>-0.2511452300720168</v>
       </c>
       <c r="J20" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K20" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02179921124174355</v>
+        <v>0.02402240715086845</v>
       </c>
       <c r="M20" t="n">
-        <v>9.697269180738722</v>
+        <v>9.726081385538386</v>
       </c>
       <c r="N20" t="n">
-        <v>154.2059848236348</v>
+        <v>154.7810796902205</v>
       </c>
       <c r="O20" t="n">
-        <v>12.41797023766907</v>
+        <v>12.44110444012992</v>
       </c>
       <c r="P20" t="n">
-        <v>329.360189170696</v>
+        <v>329.4858296102765</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34395,28 +34513,28 @@
         <v>0.0507</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4272278011649489</v>
+        <v>-0.4382954603470521</v>
       </c>
       <c r="J21" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K21" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05814981272162767</v>
+        <v>0.0611555731766118</v>
       </c>
       <c r="M21" t="n">
-        <v>9.754607527278761</v>
+        <v>9.779870480736164</v>
       </c>
       <c r="N21" t="n">
-        <v>177.8310260377021</v>
+        <v>178.1296508192955</v>
       </c>
       <c r="O21" t="n">
-        <v>13.33532999358104</v>
+        <v>13.34652204955641</v>
       </c>
       <c r="P21" t="n">
-        <v>326.2689542110812</v>
+        <v>326.3836114904631</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34473,28 +34591,28 @@
         <v>0.0745</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4458179973503473</v>
+        <v>-0.4529296631748752</v>
       </c>
       <c r="J22" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K22" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05798348912421591</v>
+        <v>0.06006095912162757</v>
       </c>
       <c r="M22" t="n">
-        <v>10.0623149131325</v>
+        <v>10.06661974631846</v>
       </c>
       <c r="N22" t="n">
-        <v>194.2336078270047</v>
+        <v>193.9159955005464</v>
       </c>
       <c r="O22" t="n">
-        <v>13.93677178642905</v>
+        <v>13.92537236487938</v>
       </c>
       <c r="P22" t="n">
-        <v>318.3183149962116</v>
+        <v>318.3919894961124</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34551,28 +34669,28 @@
         <v>0.1041</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2769448369183524</v>
+        <v>-0.2840063030578181</v>
       </c>
       <c r="J23" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K23" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02752291917529381</v>
+        <v>0.02905536290022148</v>
       </c>
       <c r="M23" t="n">
-        <v>9.86039234774185</v>
+        <v>9.866029973581394</v>
       </c>
       <c r="N23" t="n">
-        <v>163.0145765659423</v>
+        <v>162.8053980352637</v>
       </c>
       <c r="O23" t="n">
-        <v>12.76771618442164</v>
+        <v>12.7595218576271</v>
       </c>
       <c r="P23" t="n">
-        <v>309.6058595601593</v>
+        <v>309.6790140079677</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34629,28 +34747,28 @@
         <v>0.1464</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3384092272553725</v>
+        <v>-0.3426976917417875</v>
       </c>
       <c r="J24" t="n">
+        <v>274</v>
+      </c>
+      <c r="K24" t="n">
         <v>273</v>
       </c>
-      <c r="K24" t="n">
-        <v>272</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.06100458670561193</v>
+        <v>0.06284317433483499</v>
       </c>
       <c r="M24" t="n">
-        <v>8.176409247106708</v>
+        <v>8.173099163485476</v>
       </c>
       <c r="N24" t="n">
-        <v>104.974655859097</v>
+        <v>104.7304324852179</v>
       </c>
       <c r="O24" t="n">
-        <v>10.24571402387832</v>
+        <v>10.23378876493051</v>
       </c>
       <c r="P24" t="n">
-        <v>312.1969212791255</v>
+        <v>312.2417011386688</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34707,28 +34825,28 @@
         <v>0.0917</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1191865404779798</v>
+        <v>-0.1261547769061906</v>
       </c>
       <c r="J25" t="n">
+        <v>274</v>
+      </c>
+      <c r="K25" t="n">
         <v>273</v>
       </c>
-      <c r="K25" t="n">
-        <v>272</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.01693355920889927</v>
+        <v>0.01893784815930988</v>
       </c>
       <c r="M25" t="n">
-        <v>5.506908114413733</v>
+        <v>5.530109171924776</v>
       </c>
       <c r="N25" t="n">
-        <v>49.11205804386736</v>
+        <v>49.30258279151222</v>
       </c>
       <c r="O25" t="n">
-        <v>7.007999575047601</v>
+        <v>7.021579793145714</v>
       </c>
       <c r="P25" t="n">
-        <v>310.0107564286707</v>
+        <v>310.0835182877249</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34785,28 +34903,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1009690348238052</v>
+        <v>-0.1016541205947412</v>
       </c>
       <c r="J26" t="n">
+        <v>274</v>
+      </c>
+      <c r="K26" t="n">
         <v>273</v>
       </c>
-      <c r="K26" t="n">
-        <v>272</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.01036060761980362</v>
+        <v>0.0105862386715263</v>
       </c>
       <c r="M26" t="n">
-        <v>5.919261547180118</v>
+        <v>5.901687295978328</v>
       </c>
       <c r="N26" t="n">
-        <v>57.99188729183297</v>
+        <v>57.75407340444929</v>
       </c>
       <c r="O26" t="n">
-        <v>7.615240461852336</v>
+        <v>7.599610082395628</v>
       </c>
       <c r="P26" t="n">
-        <v>313.8263450411956</v>
+        <v>313.8336775996189</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34863,28 +34981,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1367107846906296</v>
+        <v>0.1405492961951907</v>
       </c>
       <c r="J27" t="n">
+        <v>274</v>
+      </c>
+      <c r="K27" t="n">
         <v>273</v>
       </c>
-      <c r="K27" t="n">
-        <v>272</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.01097940867480751</v>
+        <v>0.01167422792866701</v>
       </c>
       <c r="M27" t="n">
-        <v>7.940066110038254</v>
+        <v>7.926951027879301</v>
       </c>
       <c r="N27" t="n">
-        <v>100.2607665082181</v>
+        <v>100.0059137648569</v>
       </c>
       <c r="O27" t="n">
-        <v>10.01302983657884</v>
+        <v>10.0002956838714</v>
       </c>
       <c r="P27" t="n">
-        <v>317.864592806792</v>
+        <v>317.8245113262121</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34941,28 +35059,28 @@
         <v>0.0588</v>
       </c>
       <c r="I28" t="n">
-        <v>0.04819504561876134</v>
+        <v>0.0471663034840366</v>
       </c>
       <c r="J28" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K28" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L28" t="n">
-        <v>0.001065441469589312</v>
+        <v>0.001028456463260663</v>
       </c>
       <c r="M28" t="n">
-        <v>9.201607730329398</v>
+        <v>9.174783971000215</v>
       </c>
       <c r="N28" t="n">
-        <v>128.1775286628209</v>
+        <v>127.7142265926633</v>
       </c>
       <c r="O28" t="n">
-        <v>11.32155151305778</v>
+        <v>11.30107192228522</v>
       </c>
       <c r="P28" t="n">
-        <v>330.230411800437</v>
+        <v>330.2412491727887</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35019,28 +35137,28 @@
         <v>0.0577</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.009953805427080567</v>
+        <v>0.005166941124289012</v>
       </c>
       <c r="J29" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K29" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L29" t="n">
-        <v>4.814245243056625e-05</v>
+        <v>1.289174661878167e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>8.88623759245313</v>
+        <v>8.917402633069472</v>
       </c>
       <c r="N29" t="n">
-        <v>121.123618545856</v>
+        <v>122.3934160051262</v>
       </c>
       <c r="O29" t="n">
-        <v>11.00561759038792</v>
+        <v>11.06315578870361</v>
       </c>
       <c r="P29" t="n">
-        <v>339.4001153410986</v>
+        <v>339.2408245382023</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35097,28 +35215,28 @@
         <v>0.0459</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1841336847144812</v>
+        <v>-0.1685796919239035</v>
       </c>
       <c r="J30" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K30" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01573869956104601</v>
+        <v>0.01313934424938035</v>
       </c>
       <c r="M30" t="n">
-        <v>9.0386004951364</v>
+        <v>9.072377932655723</v>
       </c>
       <c r="N30" t="n">
-        <v>124.7980253237651</v>
+        <v>126.1540058401303</v>
       </c>
       <c r="O30" t="n">
-        <v>11.17130365372659</v>
+        <v>11.23183003077104</v>
       </c>
       <c r="P30" t="n">
-        <v>342.5546081476751</v>
+        <v>342.3907532750709</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -35175,28 +35293,28 @@
         <v>0.0523</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3019569462101571</v>
+        <v>-0.2850066610452562</v>
       </c>
       <c r="J31" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K31" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L31" t="n">
-        <v>0.04602806325254116</v>
+        <v>0.04076387637700307</v>
       </c>
       <c r="M31" t="n">
-        <v>8.976282076581773</v>
+        <v>9.034749240801167</v>
       </c>
       <c r="N31" t="n">
-        <v>111.2250496089435</v>
+        <v>112.9713868589539</v>
       </c>
       <c r="O31" t="n">
-        <v>10.54632872657322</v>
+        <v>10.62879987858243</v>
       </c>
       <c r="P31" t="n">
-        <v>342.0175344217673</v>
+        <v>341.8389701872525</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35253,28 +35371,28 @@
         <v>0.0591</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3305990950940649</v>
+        <v>-0.3185525033634598</v>
       </c>
       <c r="J32" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K32" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0474253557556007</v>
+        <v>0.04415783221850489</v>
       </c>
       <c r="M32" t="n">
-        <v>8.730562077003984</v>
+        <v>8.763817120431945</v>
       </c>
       <c r="N32" t="n">
-        <v>129.2085943795542</v>
+        <v>129.8221734827165</v>
       </c>
       <c r="O32" t="n">
-        <v>11.36699583793159</v>
+        <v>11.39395337372927</v>
       </c>
       <c r="P32" t="n">
-        <v>347.1635951323227</v>
+        <v>347.0366892773496</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35331,28 +35449,28 @@
         <v>0.0373</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2087735627613855</v>
+        <v>-0.2126731762439249</v>
       </c>
       <c r="J33" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K33" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01173450289457056</v>
+        <v>0.01225988614214435</v>
       </c>
       <c r="M33" t="n">
-        <v>11.33076858455542</v>
+        <v>11.30915075138511</v>
       </c>
       <c r="N33" t="n">
-        <v>216.0526528039113</v>
+        <v>215.3724157566105</v>
       </c>
       <c r="O33" t="n">
-        <v>14.69872963231555</v>
+        <v>14.67557207595705</v>
       </c>
       <c r="P33" t="n">
-        <v>354.8586753079023</v>
+        <v>354.8997561209764</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35390,7 +35508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH274"/>
+  <dimension ref="A1:AH275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81918,7 +82036,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>-46.663171495466486,169.05316376518059</t>
+          <t>-46.663191160715265,169.0531391076785</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -81953,22 +82071,22 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>-46.66103945352213,169.0475573295567</t>
+          <t>-46.661115412907606,169.04751502480823</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>-46.6608490939512,169.0467021901258</t>
+          <t>-46.660931096244795,169.0466565189988</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>-46.66065890143425,169.04584695703068</t>
+          <t>-46.66075290580067,169.04579460037863</t>
         </is>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>-46.66049719610324,169.0449637835666</t>
+          <t>-46.660596416079564,169.0449147149386</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -82090,7 +82208,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>-46.663171495466486,169.05316376518059</t>
+          <t>-46.663191160715265,169.0531391076785</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -82125,22 +82243,22 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>-46.66098749896956,169.0475862649979</t>
+          <t>-46.661115412907606,169.04751502480823</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>-46.66081409398866,169.04672168328523</t>
+          <t>-46.660931096244795,169.0466565189988</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>-46.66059964509461,169.0458799603222</t>
+          <t>-46.66075290580067,169.04579460037863</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>-46.66045890365208,169.04498272080775</t>
+          <t>-46.660596416079564,169.0449147149386</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -82185,7 +82303,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>-46.660715704877575,169.03680330902347</t>
+          <t>-46.660743676048504,169.03680880427598</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -82224,6 +82342,178 @@
         </is>
       </c>
       <c r="AH274" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>-46.665467771287396,169.05627177729934</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>-46.66504946919418,169.05560203077746</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>-46.664499923137754,169.05515873663708</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-46.66406609841598,169.05451576095723</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-46.6636305877643,169.05384725607382</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-46.66324791091553,169.05306795063362</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-46.66268624406288,169.05251075383043</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-46.66219942844662,169.05191520331454</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-46.661981403864566,169.05103756871952</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-46.661719731021506,169.05020573676268</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-46.661418441392534,169.0493544121741</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-46.66117952479685,169.04845868457807</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-46.66108335049542,169.0475328816344</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-46.66094150390373,169.04665072244825</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>-46.660757354220806,169.04579212278233</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>-46.66059735211693,169.04491425202613</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>-46.66038822436083,169.04403654672117</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>-46.66038425343238,169.0431018886892</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>-46.660341172195174,169.04220131034018</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>-46.66032486167203,169.04130211950402</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>-46.660344125632506,169.04040477081057</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>-46.660350633063565,169.03950676272763</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>-46.6604403156245,169.03859338615868</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>-46.660530235425455,169.0376791973284</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>-46.660726661737556,169.03680546162178</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>-46.66100939972335,169.03595510981444</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>-46.66113900874225,169.03507467348487</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>-46.66151590342078,169.03425973327276</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>-46.661673534952364,169.03341719843527</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>-46.661850457833,169.03256345380788</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>-46.66201988400787,169.0317002885808</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>-46.662109561677504,169.0308033977845</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0560/nzd0560.xlsx
+++ b/data/nzd0560/nzd0560.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH275"/>
+  <dimension ref="A1:AH276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30017,7 +30017,7 @@
         <v>296.83</v>
       </c>
       <c r="Y275" t="n">
-        <v>296.68</v>
+        <v>300.81</v>
       </c>
       <c r="Z275" t="n">
         <v>307.02</v>
@@ -30029,7 +30029,7 @@
         <v>330.05</v>
       </c>
       <c r="AC275" t="n">
-        <v>360.86</v>
+        <v>353.89</v>
       </c>
       <c r="AD275" t="n">
         <v>359.93</v>
@@ -30044,6 +30044,114 @@
         <v>343.62</v>
       </c>
       <c r="AH275" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:21:00+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>297.4</v>
+      </c>
+      <c r="C276" t="n">
+        <v>304.6</v>
+      </c>
+      <c r="D276" t="n">
+        <v>291.17</v>
+      </c>
+      <c r="E276" t="n">
+        <v>292.04</v>
+      </c>
+      <c r="F276" t="n">
+        <v>296.77</v>
+      </c>
+      <c r="G276" t="n">
+        <v>305.47</v>
+      </c>
+      <c r="H276" t="n">
+        <v>278.3</v>
+      </c>
+      <c r="I276" t="n">
+        <v>261.59</v>
+      </c>
+      <c r="J276" t="n">
+        <v>276.5</v>
+      </c>
+      <c r="K276" t="n">
+        <v>285.28</v>
+      </c>
+      <c r="L276" t="n">
+        <v>293.86</v>
+      </c>
+      <c r="M276" t="n">
+        <v>298.21</v>
+      </c>
+      <c r="N276" t="n">
+        <v>309.64</v>
+      </c>
+      <c r="O276" t="n">
+        <v>316.97</v>
+      </c>
+      <c r="P276" t="n">
+        <v>318.38</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>322.9</v>
+      </c>
+      <c r="R276" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="S276" t="n">
+        <v>313.64</v>
+      </c>
+      <c r="T276" t="n">
+        <v>305.92</v>
+      </c>
+      <c r="U276" t="n">
+        <v>299.61</v>
+      </c>
+      <c r="V276" t="n">
+        <v>295.23</v>
+      </c>
+      <c r="W276" t="n">
+        <v>291.14</v>
+      </c>
+      <c r="X276" t="n">
+        <v>296.29</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>301.74</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>306.72</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>325.43</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>328.41</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>348.35</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>353.67</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>352.09</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>351.05</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="AH276" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30060,7 +30168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32863,6 +32971,16 @@
       </c>
       <c r="B280" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -33031,28 +33149,28 @@
         <v>0.1765</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6834641541707314</v>
+        <v>-0.6821780549914268</v>
       </c>
       <c r="J2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K2" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2285969786220402</v>
+        <v>0.2292751719137663</v>
       </c>
       <c r="M2" t="n">
-        <v>7.570312254641819</v>
+        <v>7.548548061989102</v>
       </c>
       <c r="N2" t="n">
-        <v>94.34680170840613</v>
+        <v>94.01399407737125</v>
       </c>
       <c r="O2" t="n">
-        <v>9.713228181629738</v>
+        <v>9.696081377410735</v>
       </c>
       <c r="P2" t="n">
-        <v>314.0120827613522</v>
+        <v>313.9986192815784</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33109,28 +33227,28 @@
         <v>0.0501</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.28636686994261</v>
+        <v>-1.282142108166457</v>
       </c>
       <c r="J3" t="n">
+        <v>275</v>
+      </c>
+      <c r="K3" t="n">
         <v>274</v>
       </c>
-      <c r="K3" t="n">
-        <v>273</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3424450752512828</v>
+        <v>0.3425343579292817</v>
       </c>
       <c r="M3" t="n">
-        <v>10.74460769508673</v>
+        <v>10.73002642192477</v>
       </c>
       <c r="N3" t="n">
-        <v>192.2787267879052</v>
+        <v>191.7171489496969</v>
       </c>
       <c r="O3" t="n">
-        <v>13.86646049963383</v>
+        <v>13.84619619064012</v>
       </c>
       <c r="P3" t="n">
-        <v>333.163578452012</v>
+        <v>333.1197221217147</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33187,28 +33305,28 @@
         <v>0.0344</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.065846806047926</v>
+        <v>-1.068100341023668</v>
       </c>
       <c r="J4" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K4" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2674758159403682</v>
+        <v>0.2697967279866124</v>
       </c>
       <c r="M4" t="n">
-        <v>10.6504519118047</v>
+        <v>10.62142578815144</v>
       </c>
       <c r="N4" t="n">
-        <v>185.5454859799738</v>
+        <v>184.9021758645402</v>
       </c>
       <c r="O4" t="n">
-        <v>13.6215082123814</v>
+        <v>13.59787394648664</v>
       </c>
       <c r="P4" t="n">
-        <v>323.2722395602586</v>
+        <v>323.2958754629099</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33265,28 +33383,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7154686295300848</v>
+        <v>-0.7146393769463456</v>
       </c>
       <c r="J5" t="n">
+        <v>275</v>
+      </c>
+      <c r="K5" t="n">
         <v>274</v>
       </c>
-      <c r="K5" t="n">
-        <v>273</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1830742039878184</v>
+        <v>0.1838798052122141</v>
       </c>
       <c r="M5" t="n">
-        <v>9.483686751670295</v>
+        <v>9.452917976240425</v>
       </c>
       <c r="N5" t="n">
-        <v>137.0283487241554</v>
+        <v>136.5335789765981</v>
       </c>
       <c r="O5" t="n">
-        <v>11.70591084555813</v>
+        <v>11.68475840471672</v>
       </c>
       <c r="P5" t="n">
-        <v>310.1747397026999</v>
+        <v>310.1660805097434</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33343,28 +33461,28 @@
         <v>0.0596</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6206915840717606</v>
+        <v>-0.6184655845809939</v>
       </c>
       <c r="J6" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K6" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1679300537353733</v>
+        <v>0.1679576545818473</v>
       </c>
       <c r="M6" t="n">
-        <v>8.801325404349987</v>
+        <v>8.77946585052805</v>
       </c>
       <c r="N6" t="n">
-        <v>115.2996005390367</v>
+        <v>114.919103380231</v>
       </c>
       <c r="O6" t="n">
-        <v>10.73776515570334</v>
+        <v>10.72003280686356</v>
       </c>
       <c r="P6" t="n">
-        <v>310.2799589355536</v>
+        <v>310.2568523908248</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33421,28 +33539,28 @@
         <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5437493701626536</v>
+        <v>-0.5320122463300971</v>
       </c>
       <c r="J7" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K7" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1377360516900223</v>
+        <v>0.1324460684809999</v>
       </c>
       <c r="M7" t="n">
-        <v>8.006086093018665</v>
+        <v>8.027997585337166</v>
       </c>
       <c r="N7" t="n">
-        <v>112.5419880996946</v>
+        <v>113.1947567992622</v>
       </c>
       <c r="O7" t="n">
-        <v>10.60858087114835</v>
+        <v>10.63930245830347</v>
       </c>
       <c r="P7" t="n">
-        <v>303.0669394779442</v>
+        <v>302.9458008745759</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33499,28 +33617,28 @@
         <v>0.0326</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.778890379660737</v>
+        <v>-0.7749796961918808</v>
       </c>
       <c r="J8" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K8" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1169210931650683</v>
+        <v>0.1166511290373314</v>
       </c>
       <c r="M8" t="n">
-        <v>13.06658012450737</v>
+        <v>13.03807012764169</v>
       </c>
       <c r="N8" t="n">
-        <v>276.4297832326665</v>
+        <v>275.519346549094</v>
       </c>
       <c r="O8" t="n">
-        <v>16.62617764949799</v>
+        <v>16.59877545330058</v>
       </c>
       <c r="P8" t="n">
-        <v>293.7268272047771</v>
+        <v>293.6861688379341</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33577,28 +33695,28 @@
         <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3280211479072</v>
+        <v>-1.326228983185604</v>
       </c>
       <c r="J9" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K9" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1889822128937617</v>
+        <v>0.1897825129966925</v>
       </c>
       <c r="M9" t="n">
-        <v>16.37303232342395</v>
+        <v>16.32061058469962</v>
       </c>
       <c r="N9" t="n">
-        <v>442.0049483183952</v>
+        <v>440.3730466007437</v>
       </c>
       <c r="O9" t="n">
-        <v>21.02391372505118</v>
+        <v>20.98506722888311</v>
       </c>
       <c r="P9" t="n">
-        <v>294.9887633283241</v>
+        <v>294.9696719615296</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33655,28 +33773,28 @@
         <v>0.0409</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.342486951212069</v>
+        <v>-0.3469153849887263</v>
       </c>
       <c r="J10" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K10" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01751823405040531</v>
+        <v>0.01809425782037255</v>
       </c>
       <c r="M10" t="n">
-        <v>16.21808344564881</v>
+        <v>16.1830855415753</v>
       </c>
       <c r="N10" t="n">
-        <v>398.229558081821</v>
+        <v>396.8879327094933</v>
       </c>
       <c r="O10" t="n">
-        <v>19.95568986734914</v>
+        <v>19.9220463986382</v>
       </c>
       <c r="P10" t="n">
-        <v>292.2279863998911</v>
+        <v>292.2744464046252</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33733,28 +33851,28 @@
         <v>0.0649</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.29123023754884</v>
+        <v>-1.285264925330616</v>
       </c>
       <c r="J11" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K11" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L11" t="n">
-        <v>0.223387829596982</v>
+        <v>0.2230276832660911</v>
       </c>
       <c r="M11" t="n">
-        <v>14.79828151849519</v>
+        <v>14.768279133231</v>
       </c>
       <c r="N11" t="n">
-        <v>352.6966778300753</v>
+        <v>351.6625483002496</v>
       </c>
       <c r="O11" t="n">
-        <v>18.78022038821896</v>
+        <v>18.75266776488747</v>
       </c>
       <c r="P11" t="n">
-        <v>311.5811414924147</v>
+        <v>311.5198071922602</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33811,28 +33929,28 @@
         <v>0.1385</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5384476497244017</v>
+        <v>-0.5424076268322545</v>
       </c>
       <c r="J12" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K12" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06861329688676465</v>
+        <v>0.07002335735128096</v>
       </c>
       <c r="M12" t="n">
-        <v>12.1590975376741</v>
+        <v>12.1405423192952</v>
       </c>
       <c r="N12" t="n">
-        <v>237.7132539672562</v>
+        <v>236.9715513370603</v>
       </c>
       <c r="O12" t="n">
-        <v>15.4179523273117</v>
+        <v>15.39388032099315</v>
       </c>
       <c r="P12" t="n">
-        <v>314.2657087478668</v>
+        <v>314.3068145021792</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33889,28 +34007,28 @@
         <v>0.0963</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6482119006428005</v>
+        <v>-0.644077424710675</v>
       </c>
       <c r="J13" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K13" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1005666236641138</v>
+        <v>0.1000776973655034</v>
       </c>
       <c r="M13" t="n">
-        <v>12.33297366484026</v>
+        <v>12.31205045371427</v>
       </c>
       <c r="N13" t="n">
-        <v>228.7234898551368</v>
+        <v>228.0071971596357</v>
       </c>
       <c r="O13" t="n">
-        <v>15.12360703850562</v>
+        <v>15.09990719043119</v>
       </c>
       <c r="P13" t="n">
-        <v>309.7644763611552</v>
+        <v>309.7219691919979</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33967,28 +34085,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9381681984368584</v>
+        <v>-0.9225741143943061</v>
       </c>
       <c r="J14" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K14" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L14" t="n">
-        <v>0.138891803208033</v>
+        <v>0.135210313867168</v>
       </c>
       <c r="M14" t="n">
-        <v>14.82181506408626</v>
+        <v>14.86112960543743</v>
       </c>
       <c r="N14" t="n">
-        <v>334.0772413331371</v>
+        <v>334.6867688503404</v>
       </c>
       <c r="O14" t="n">
-        <v>18.27777998918734</v>
+        <v>18.29444639365565</v>
       </c>
       <c r="P14" t="n">
-        <v>312.6143676234126</v>
+        <v>312.4542662792836</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34045,28 +34163,28 @@
         <v>0.0604</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7198598197084449</v>
+        <v>-0.7057978874069818</v>
       </c>
       <c r="J15" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K15" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L15" t="n">
-        <v>0.113200745219038</v>
+        <v>0.1094390885323787</v>
       </c>
       <c r="M15" t="n">
-        <v>12.63145488302327</v>
+        <v>12.65848919987406</v>
       </c>
       <c r="N15" t="n">
-        <v>246.9667328327606</v>
+        <v>247.618240431475</v>
       </c>
       <c r="O15" t="n">
-        <v>15.71517524028162</v>
+        <v>15.73589020143045</v>
       </c>
       <c r="P15" t="n">
-        <v>315.7169821365119</v>
+        <v>315.5716130916426</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34123,28 +34241,28 @@
         <v>0.0507</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6312780963865264</v>
+        <v>-0.6205968378487517</v>
       </c>
       <c r="J16" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K16" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07882324622499282</v>
+        <v>0.07670135840206938</v>
       </c>
       <c r="M16" t="n">
-        <v>13.24217032585482</v>
+        <v>13.24735520499195</v>
       </c>
       <c r="N16" t="n">
-        <v>281.3032661490923</v>
+        <v>281.1731091148181</v>
       </c>
       <c r="O16" t="n">
-        <v>16.7720978458001</v>
+        <v>16.76821723126278</v>
       </c>
       <c r="P16" t="n">
-        <v>319.6980101573037</v>
+        <v>319.587135478677</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34201,28 +34319,28 @@
         <v>0.0455</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4042937912689518</v>
+        <v>0.4034575880651214</v>
       </c>
       <c r="J17" t="n">
+        <v>275</v>
+      </c>
+      <c r="K17" t="n">
         <v>274</v>
       </c>
-      <c r="K17" t="n">
-        <v>273</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.02629465891058191</v>
+        <v>0.02638578245309631</v>
       </c>
       <c r="M17" t="n">
-        <v>13.93271675110299</v>
+        <v>13.88707903525566</v>
       </c>
       <c r="N17" t="n">
-        <v>365.7485013198799</v>
+        <v>364.4191347649175</v>
       </c>
       <c r="O17" t="n">
-        <v>19.12455231684862</v>
+        <v>19.08976518359819</v>
       </c>
       <c r="P17" t="n">
-        <v>313.1984389302727</v>
+        <v>313.2071289207458</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34279,28 +34397,28 @@
         <v>0.0552</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2053878117724964</v>
+        <v>0.1941231632931866</v>
       </c>
       <c r="J18" t="n">
+        <v>275</v>
+      </c>
+      <c r="K18" t="n">
         <v>274</v>
       </c>
-      <c r="K18" t="n">
-        <v>273</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.02273907860509539</v>
+        <v>0.02033532337965338</v>
       </c>
       <c r="M18" t="n">
-        <v>8.398268071618183</v>
+        <v>8.427123502795942</v>
       </c>
       <c r="N18" t="n">
-        <v>109.710309574515</v>
+        <v>110.3064220421123</v>
       </c>
       <c r="O18" t="n">
-        <v>10.47426892792595</v>
+        <v>10.5026864202504</v>
       </c>
       <c r="P18" t="n">
-        <v>330.0139254104697</v>
+        <v>330.1308612687658</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34357,28 +34475,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.02074195230628416</v>
+        <v>-0.03064525931035555</v>
       </c>
       <c r="J19" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K19" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0002414824537597671</v>
+        <v>0.0005272826542964681</v>
       </c>
       <c r="M19" t="n">
-        <v>8.312380500632678</v>
+        <v>8.340905432571073</v>
       </c>
       <c r="N19" t="n">
-        <v>107.5854337939397</v>
+        <v>107.9616678819064</v>
       </c>
       <c r="O19" t="n">
-        <v>10.37233984180714</v>
+        <v>10.39046042684858</v>
       </c>
       <c r="P19" t="n">
-        <v>328.8099708314214</v>
+        <v>328.9127701389687</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34435,28 +34553,28 @@
         <v>0.0559</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2511452300720168</v>
+        <v>-0.2625140235328147</v>
       </c>
       <c r="J20" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K20" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02402240715086845</v>
+        <v>0.02621847574385128</v>
       </c>
       <c r="M20" t="n">
-        <v>9.726081385538386</v>
+        <v>9.751769106772286</v>
       </c>
       <c r="N20" t="n">
-        <v>154.7810796902205</v>
+        <v>155.2296337800524</v>
       </c>
       <c r="O20" t="n">
-        <v>12.44110444012992</v>
+        <v>12.45911849931817</v>
       </c>
       <c r="P20" t="n">
-        <v>329.4858296102765</v>
+        <v>329.6038411083485</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34513,28 +34631,28 @@
         <v>0.0507</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4382954603470521</v>
+        <v>-0.4484100396987742</v>
       </c>
       <c r="J21" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K21" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0611555731766118</v>
+        <v>0.06402116928119683</v>
       </c>
       <c r="M21" t="n">
-        <v>9.779870480736164</v>
+        <v>9.800662693999708</v>
       </c>
       <c r="N21" t="n">
-        <v>178.1296508192955</v>
+        <v>178.2824547406223</v>
       </c>
       <c r="O21" t="n">
-        <v>13.34652204955641</v>
+        <v>13.35224530708683</v>
       </c>
       <c r="P21" t="n">
-        <v>326.3836114904631</v>
+        <v>326.4886038685709</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34591,28 +34709,28 @@
         <v>0.0745</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4529296631748752</v>
+        <v>-0.4603259215705645</v>
       </c>
       <c r="J22" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K22" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L22" t="n">
-        <v>0.06006095912162757</v>
+        <v>0.06223675605962997</v>
       </c>
       <c r="M22" t="n">
-        <v>10.06661974631846</v>
+        <v>10.07248799689181</v>
       </c>
       <c r="N22" t="n">
-        <v>193.9159955005464</v>
+        <v>193.6389175501304</v>
       </c>
       <c r="O22" t="n">
-        <v>13.92537236487938</v>
+        <v>13.91542013559527</v>
       </c>
       <c r="P22" t="n">
-        <v>318.3919894961124</v>
+        <v>318.4687648844959</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34669,28 +34787,28 @@
         <v>0.1041</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2840063030578181</v>
+        <v>-0.2913652585190165</v>
       </c>
       <c r="J23" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K23" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02905536290022148</v>
+        <v>0.03068569372272045</v>
       </c>
       <c r="M23" t="n">
-        <v>9.866029973581394</v>
+        <v>9.87328513674745</v>
       </c>
       <c r="N23" t="n">
-        <v>162.8053980352637</v>
+        <v>162.6371424764557</v>
       </c>
       <c r="O23" t="n">
-        <v>12.7595218576271</v>
+        <v>12.75292682000707</v>
       </c>
       <c r="P23" t="n">
-        <v>309.6790140079677</v>
+        <v>309.7554021806632</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34747,28 +34865,28 @@
         <v>0.1464</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3426976917417875</v>
+        <v>-0.3472686764446061</v>
       </c>
       <c r="J24" t="n">
+        <v>275</v>
+      </c>
+      <c r="K24" t="n">
         <v>274</v>
       </c>
-      <c r="K24" t="n">
-        <v>273</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.06284317433483499</v>
+        <v>0.06479720216182405</v>
       </c>
       <c r="M24" t="n">
-        <v>8.173099163485476</v>
+        <v>8.171458635653645</v>
       </c>
       <c r="N24" t="n">
-        <v>104.7304324852179</v>
+        <v>104.5094345989346</v>
       </c>
       <c r="O24" t="n">
-        <v>10.23378876493051</v>
+        <v>10.22298560103332</v>
       </c>
       <c r="P24" t="n">
-        <v>312.2417011386688</v>
+        <v>312.2895253373919</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34825,28 +34943,28 @@
         <v>0.0917</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1261547769061906</v>
+        <v>-0.1267133015265746</v>
       </c>
       <c r="J25" t="n">
+        <v>275</v>
+      </c>
+      <c r="K25" t="n">
         <v>274</v>
       </c>
-      <c r="K25" t="n">
-        <v>273</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.01893784815930988</v>
+        <v>0.01930647582894252</v>
       </c>
       <c r="M25" t="n">
-        <v>5.530109171924776</v>
+        <v>5.513316264477313</v>
       </c>
       <c r="N25" t="n">
-        <v>49.30258279151222</v>
+        <v>48.9721810548796</v>
       </c>
       <c r="O25" t="n">
-        <v>7.021579793145714</v>
+        <v>6.998012650380078</v>
       </c>
       <c r="P25" t="n">
-        <v>310.0835182877249</v>
+        <v>310.0894205801697</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34903,28 +35021,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1016541205947412</v>
+        <v>-0.1046391948548511</v>
       </c>
       <c r="J26" t="n">
+        <v>275</v>
+      </c>
+      <c r="K26" t="n">
         <v>274</v>
       </c>
-      <c r="K26" t="n">
-        <v>273</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.0105862386715263</v>
+        <v>0.01128293777634937</v>
       </c>
       <c r="M26" t="n">
-        <v>5.901687295978328</v>
+        <v>5.898784535948231</v>
       </c>
       <c r="N26" t="n">
-        <v>57.75407340444929</v>
+        <v>57.61205221712837</v>
       </c>
       <c r="O26" t="n">
-        <v>7.599610082395628</v>
+        <v>7.590260352394268</v>
       </c>
       <c r="P26" t="n">
-        <v>313.8336775996189</v>
+        <v>313.8649091162175</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34981,28 +35099,28 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1405492961951907</v>
+        <v>0.1431491145577168</v>
       </c>
       <c r="J27" t="n">
+        <v>275</v>
+      </c>
+      <c r="K27" t="n">
         <v>274</v>
       </c>
-      <c r="K27" t="n">
-        <v>273</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.01167422792866701</v>
+        <v>0.01219157323696429</v>
       </c>
       <c r="M27" t="n">
-        <v>7.926951027879301</v>
+        <v>7.909178504113216</v>
       </c>
       <c r="N27" t="n">
-        <v>100.0059137648569</v>
+        <v>99.69308563565174</v>
       </c>
       <c r="O27" t="n">
-        <v>10.0002956838714</v>
+        <v>9.984642489125575</v>
       </c>
       <c r="P27" t="n">
-        <v>317.8245113262121</v>
+        <v>317.7973105723053</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35059,28 +35177,28 @@
         <v>0.0588</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0471663034840366</v>
+        <v>0.04501873604411687</v>
       </c>
       <c r="J28" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K28" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L28" t="n">
-        <v>0.001028456463260663</v>
+        <v>0.0009440813765916323</v>
       </c>
       <c r="M28" t="n">
-        <v>9.174783971000215</v>
+        <v>9.155699347771941</v>
       </c>
       <c r="N28" t="n">
-        <v>127.7142265926633</v>
+        <v>127.2814062827657</v>
       </c>
       <c r="O28" t="n">
-        <v>11.30107192228522</v>
+        <v>11.28190614580558</v>
       </c>
       <c r="P28" t="n">
-        <v>330.2412491727887</v>
+        <v>330.2639171402197</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35137,28 +35255,28 @@
         <v>0.0577</v>
       </c>
       <c r="I29" t="n">
-        <v>0.005166941124289012</v>
+        <v>0.00656884013743423</v>
       </c>
       <c r="J29" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K29" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L29" t="n">
-        <v>1.289174661878167e-05</v>
+        <v>2.110714096947852e-05</v>
       </c>
       <c r="M29" t="n">
-        <v>8.917402633069472</v>
+        <v>8.890636156026158</v>
       </c>
       <c r="N29" t="n">
-        <v>122.3934160051262</v>
+        <v>121.321231960283</v>
       </c>
       <c r="O29" t="n">
-        <v>11.06315578870361</v>
+        <v>11.01459177456355</v>
       </c>
       <c r="P29" t="n">
-        <v>339.2408245382023</v>
+        <v>339.2259273254984</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35215,28 +35333,28 @@
         <v>0.0459</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1685796919239035</v>
+        <v>-0.1576365632356168</v>
       </c>
       <c r="J30" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K30" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01313934424938035</v>
+        <v>0.01151453492470667</v>
       </c>
       <c r="M30" t="n">
-        <v>9.072377932655723</v>
+        <v>9.088592737973761</v>
       </c>
       <c r="N30" t="n">
-        <v>126.1540058401303</v>
+        <v>126.6006121916999</v>
       </c>
       <c r="O30" t="n">
-        <v>11.23183003077104</v>
+        <v>11.25169374768527</v>
       </c>
       <c r="P30" t="n">
-        <v>342.3907532750709</v>
+        <v>342.2752465486756</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -35293,28 +35411,28 @@
         <v>0.0523</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2850066610452562</v>
+        <v>-0.2726021480072586</v>
       </c>
       <c r="J31" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K31" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L31" t="n">
-        <v>0.04076387637700307</v>
+        <v>0.03733159888800774</v>
       </c>
       <c r="M31" t="n">
-        <v>9.034749240801167</v>
+        <v>9.068093183034385</v>
       </c>
       <c r="N31" t="n">
-        <v>112.9713868589539</v>
+        <v>113.7251914509727</v>
       </c>
       <c r="O31" t="n">
-        <v>10.62879987858243</v>
+        <v>10.66420139771247</v>
       </c>
       <c r="P31" t="n">
-        <v>341.8389701872525</v>
+        <v>341.7080382815461</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35371,28 +35489,28 @@
         <v>0.0591</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3185525033634598</v>
+        <v>-0.3098260788357629</v>
       </c>
       <c r="J32" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K32" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L32" t="n">
-        <v>0.04415783221850489</v>
+        <v>0.042005481745232</v>
       </c>
       <c r="M32" t="n">
-        <v>8.763817120431945</v>
+        <v>8.778836247955647</v>
       </c>
       <c r="N32" t="n">
-        <v>129.8221734827165</v>
+        <v>129.9244835111782</v>
       </c>
       <c r="O32" t="n">
-        <v>11.39395337372927</v>
+        <v>11.39844215281975</v>
       </c>
       <c r="P32" t="n">
-        <v>347.0366892773496</v>
+        <v>346.944580269127</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35449,28 +35567,28 @@
         <v>0.0373</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2126731762439249</v>
+        <v>-0.2176771489431923</v>
       </c>
       <c r="J33" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K33" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L33" t="n">
-        <v>0.01225988614214435</v>
+        <v>0.01292390029550561</v>
       </c>
       <c r="M33" t="n">
-        <v>11.30915075138511</v>
+        <v>11.2932346078007</v>
       </c>
       <c r="N33" t="n">
-        <v>215.3724157566105</v>
+        <v>214.7735137050875</v>
       </c>
       <c r="O33" t="n">
-        <v>14.67557207595705</v>
+        <v>14.65515314505746</v>
       </c>
       <c r="P33" t="n">
-        <v>354.8997561209764</v>
+        <v>354.9525739687719</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35508,7 +35626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH275"/>
+  <dimension ref="A1:AH276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82470,7 +82588,7 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>-46.660530235425455,169.0376791973284</t>
+          <t>-46.660567082809365,169.03768578114514</t>
         </is>
       </c>
       <c r="Z275" t="inlineStr">
@@ -82490,7 +82608,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>-46.66151590342078,169.03425973327276</t>
+          <t>-46.66145436009664,169.03424267275471</t>
         </is>
       </c>
       <c r="AD275" t="inlineStr">
@@ -82514,6 +82632,178 @@
         </is>
       </c>
       <c r="AH275" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:21:00+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>-46.66546533982224,169.0562759727389</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>-46.66504952708579,169.05560193088635</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>-46.664514280202894,169.0551339638369</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-46.66406181448093,169.05452315281062</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-46.66362226366085,169.05386061581947</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-46.663227769363296,169.05309320542935</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-46.66267225422983,169.05252543536687</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-46.662207079110246,169.05190717437412</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-46.661972295987965,169.05104712704195</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-46.66169284472291,169.05023395306068</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-46.66139309146029,169.04937602547136</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>-46.66116950902086,169.04846484541247</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>-46.661060856444934,169.0475454094468</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-46.660921779711096,169.0466617078445</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>-46.660733013807835,169.0458056794361</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>-46.660569270994465,169.0449281393935</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>-46.66037770123577,169.04403848292299</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>-46.660374281788066,169.04310137236945</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>-46.66034808946039,169.0422016684288</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>-46.66033456380802,169.04130262164722</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>-46.66033837621994,169.04040447330982</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>-46.66034479381778,169.03950646064507</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>-46.660435474397964,169.03859287224657</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>-46.66057538016213,169.03768726370055</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>-46.660723989332695,169.03680493659775</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>-46.66099425608826,169.03595213482976</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>-46.66112439958064,169.03507180365892</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>-46.66140544330683,169.03422911248228</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>-46.661619199910014,169.03339593935664</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>-46.66179755177783,169.03254107821394</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>-46.661981132197724,169.03168389966578</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>-46.66209471685923,169.03079711978964</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
